--- a/docs/concept-v1.01.xlsx
+++ b/docs/concept-v1.01.xlsx
@@ -3235,7 +3235,7 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>F1 F2 F3 F4 F5 F6 F8 F10</t>
+          <t>F1 F2 F3 F4 F5 F6 F8 F10 F21</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
